--- a/device-model-indicators/飞轮_指标库_20260225.xlsx
+++ b/device-model-indicators/飞轮_指标库_20260225.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="256" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="308" uniqueCount="55">
   <si>
     <t>型号 Model</t>
   </si>
@@ -1765,12 +1765,8 @@
       <c r="D38" s="0">
         <v>6000</v>
       </c>
-      <c r="E38" s="0">
-        <v>1</v>
-      </c>
-      <c r="F38" s="0">
-        <v>5.0000000000000002e-05</v>
-      </c>
+      <c r="E38" s="0"/>
+      <c r="F38" s="0"/>
       <c r="G38" s="0">
         <v>2</v>
       </c>
@@ -1783,12 +1779,8 @@
       <c r="J38" s="0">
         <v>28</v>
       </c>
-      <c r="K38" s="0">
-        <v>-20</v>
-      </c>
-      <c r="L38" s="0">
-        <v>50</v>
-      </c>
+      <c r="K38" s="0"/>
+      <c r="L38" s="0"/>
       <c r="M38" s="0">
         <v>8</v>
       </c>
@@ -1807,21 +1799,11 @@
       <c r="D39" s="0">
         <v>6000</v>
       </c>
-      <c r="E39" s="0">
-        <v>1</v>
-      </c>
-      <c r="F39" s="0">
-        <v>0.00020000000000000001</v>
-      </c>
-      <c r="G39" s="0">
-        <v>5</v>
-      </c>
-      <c r="H39" s="0">
-        <v>8</v>
-      </c>
-      <c r="I39" s="0">
-        <v>100</v>
-      </c>
+      <c r="E39" s="0"/>
+      <c r="F39" s="0"/>
+      <c r="G39" s="0"/>
+      <c r="H39" s="0"/>
+      <c r="I39" s="0"/>
       <c r="J39" s="0">
         <v>28</v>
       </c>

--- a/device-model-indicators/飞轮_指标库_20260225.xlsx
+++ b/device-model-indicators/飞轮_指标库_20260225.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="308" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="360" uniqueCount="57">
   <si>
     <t>型号 Model</t>
   </si>
@@ -178,6 +178,12 @@
   </si>
   <si>
     <t>YYMQ9WHL9Nms</t>
+  </si>
+  <si>
+    <t>LX630WHL2Nms</t>
+  </si>
+  <si>
+    <t>YYMQ9WHL8Nms</t>
   </si>
 </sst>
 </file>
@@ -226,7 +232,7 @@
   <dimension ref="A1:N39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" customWidth="true"/>
+    <col min="1" max="1" width="14.44140625" customWidth="true"/>
     <col min="2" max="2" width="29.77734375" customWidth="true"/>
     <col min="3" max="3" width="23" customWidth="true"/>
     <col min="4" max="4" width="22.6640625" customWidth="true"/>
@@ -496,7 +502,7 @@
         <v>15</v>
       </c>
       <c r="C7" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="D7" s="0">
         <v>4050</v>
@@ -618,7 +624,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="0">
-        <v>0.14999999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="D10" s="0">
         <v>3500</v>
@@ -856,7 +862,7 @@
       <c r="E16" s="0"/>
       <c r="F16" s="0"/>
       <c r="G16" s="0">
-        <v>8.0999999999999996</v>
+        <v>8.0999999999999997</v>
       </c>
       <c r="H16" s="0">
         <v>25</v>
@@ -1318,7 +1324,7 @@
         <v>3.0000000000000001e-05</v>
       </c>
       <c r="G27" s="0">
-        <v>0.55000000000000004</v>
+        <v>0.55000000000000005</v>
       </c>
       <c r="H27" s="0">
         <v>4</v>
@@ -1754,13 +1760,13 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B38" s="0">
-        <v>2.3999999999999999</v>
+        <v>2</v>
       </c>
       <c r="C38" s="0">
-        <v>0.12</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D38" s="0">
         <v>6000</v>
@@ -1768,13 +1774,13 @@
       <c r="E38" s="0"/>
       <c r="F38" s="0"/>
       <c r="G38" s="0">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="H38" s="0">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I38" s="0">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J38" s="0">
         <v>28</v>
@@ -1782,19 +1788,19 @@
       <c r="K38" s="0"/>
       <c r="L38" s="0"/>
       <c r="M38" s="0">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N38" s="0"/>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B39" s="0">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C39" s="0">
-        <v>0.12</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D39" s="0">
         <v>6000</v>
@@ -1814,7 +1820,7 @@
         <v>45</v>
       </c>
       <c r="M39" s="0">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N39" s="0"/>
     </row>
